--- a/temp/template.xlsx
+++ b/temp/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuno\Dailyreport_test\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AE969D-D7CE-4E16-94EE-496F0E9C686D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC214855-A176-47BE-9C35-69A399B9C48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="temp" sheetId="33" r:id="rId1"/>
@@ -461,6 +461,9 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -477,9 +480,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -849,11 +849,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="22"/>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="26"/>
+      <c r="C1" s="27"/>
       <c r="D1" s="18" t="s">
         <v>41</v>
       </c>
@@ -900,11 +900,11 @@
       <c r="AS1" s="14"/>
     </row>
     <row r="2" spans="1:45" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="23"/>
-      <c r="B2" s="25" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
@@ -949,7 +949,7 @@
       <c r="AS2" s="17"/>
     </row>
     <row r="3" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="24"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="3" t="s">
         <v>37</v>
       </c>
@@ -2532,7 +2532,7 @@
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
-      <c r="L35" s="21"/>
+      <c r="L35" s="20"/>
       <c r="M35" s="20"/>
       <c r="N35" s="20"/>
       <c r="O35" s="20"/>
@@ -2787,13 +2787,13 @@
       <c r="AS39" s="15"/>
     </row>
     <row r="40" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="28"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="22"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
@@ -2813,36 +2813,36 @@
       <c r="AJ40" s="2"/>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="1:45" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
       <c r="K43" s="9"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -2887,9 +2887,9 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -2934,9 +2934,9 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
@@ -5748,14 +5748,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="J45"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B1:C1"/>
@@ -5772,6 +5764,14 @@
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="J41"/>
     <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="J45"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="J43"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/temp/template.xlsx
+++ b/temp/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mizuno\Dailyreport_test\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5325A5-B408-465E-966C-A51CECC6F306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F583958D-07F1-457C-BC07-CB689B64FA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31425" yWindow="1065" windowWidth="24030" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="2115" windowWidth="24030" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="temp" sheetId="33" r:id="rId1"/>
@@ -297,7 +297,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="13"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -480,7 +480,7 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -501,7 +501,7 @@
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2754,7 +2754,7 @@
       <c r="A39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="28">
         <f>B38+C38</f>
         <v>0</v>
       </c>
@@ -2804,13 +2804,13 @@
       <c r="AS39" s="14"/>
     </row>
     <row r="40" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
       <c r="N40" s="27"/>
-      <c r="O40" s="28"/>
+      <c r="O40" s="21"/>
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
       <c r="V40" s="2"/>
@@ -5416,13 +5416,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="H40:I40"/>
     <mergeCell ref="J40"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="F40:G40"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
